--- a/excel_files/CHP_12_how_to_build_an_xmr_chart.xlsx
+++ b/excel_files/CHP_12_how_to_build_an_xmr_chart.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\OneDrive\Documents\GitHub\the-virus-of-variation\excel_files_2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\OneDrive\Documents\GitHub\the-virus-of-variation\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC193D5-CBBD-4D68-929C-8D4832691FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C37380A-8367-4AF8-85AC-648698585FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="20" r:id="rId1"/>
@@ -1177,117 +1177,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">To calculate the moving ranges, begin by selecting cell </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t>F4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t xml:space="preserve"> and entering the equation </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t>= ROUND(ABS(B3 - B4), 2)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t xml:space="preserve">. This formula calculates the absolute value of the difference between cells B3 (14.6) and B4 (7.5). Because we are working inside a table, Excel automatically copies the formula to all other rows in column F, calculating all of the values of the moving range. 
-Since we are only concerned with the magnitude of the difference between values, the formula wraps the subtraction between successive cells in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t>ABS()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t xml:space="preserve"> function. This ensures the result of the subtraction is always positive, never negative. The </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t>ABS()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t xml:space="preserve"> function is then wrapped in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t>ROUND()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t xml:space="preserve"> so we can specify the result is returned to 2 decimal places.
-When the formula is entered correctly, the moving range in cell F4 should be 7.1. 
-Note that cell F3 returns </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t>#VALUE!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t xml:space="preserve"> This error is Excel's way of telling you that one of the cells in the cormula contains text instead of a number. That is, Excel has attempted to subtract the numeric value in B3 of 14.6 from the text value in B2 of Rate. Since arithmetic between text and numbers is not possible #VALUE! is returned. Select F4 and press delete to remove the error.  
-Note that the values in cells F14 and F15 are also highlighted. Since B14 contains no value, the calculated moving ranges in cells F14 and F15 are erroneous. If they are not deleted they will inflate the average moving range. Thus, to avoid calculating an inflated average moving range, select cells F14 and F15 and press delete.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">The XmR chart requires the calculation of three process limits: the Upper Process Limit (UPL) , the Lower Process Limit (LPL) , and the Upper Range Limit (URL). The generic formulas for these limits are:
 UPL = Mean + (2.660*Ave. mR)
 LPL = Mean - (2.660*Ave. mR)
@@ -1399,53 +1288,6 @@
       <t>.
 An unpredictable process, as oppsed to a predictable process, is influenced by both common causes of routine variation and assignable causes of exceptional variation. This means that, moving forward, all that we can expect from this process is the unexpected.
 Until the assignable causes of exceptional variation are identified, understood, and eliminated, this process will continue to produce values outside of the specification limits.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Constructing an XmR chart in Excel is achieved in two steps: constructing the X chart and constructing the mR chart. We will begin by constructing the X chart. 
-To construct the X chart select cells A2 through E101. With these cells selected, navigate to the toolbar and select </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t>INSERT &gt; CHARTS &gt; LINE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t xml:space="preserve">.
-To construct the mR chart select cells F2 through H101. With these cells selected, navigate to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t>INSERT &gt; CHARTS &gt; LINE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t>.
-With the charts inserted, format them so that:
-1) Delete the Chart Titles, Legends, and horizontal grid lines. 
-2) Change all of the process limits to a dashed line style and make the color red.
-3) Change the line color for the mean and the average moving range to black. 
-4) Change the marker type for the rates and moving ranges to built in type circle and size 6.
-Additionally, establish conditional formating paramters for the Rate column (B4:B102) so that any cell with a death-to-birth rate that is greater than the UPL or equal to the LPL is highlighted with a light red fill and a dark red text. Also establish conditional formatting for any moving range greater than the URL in the mR column (F4:F101).</t>
     </r>
   </si>
   <si>
@@ -1629,99 +1471,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">To calculate the average moving range, select cell G3 and enter the formula:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t xml:space="preserve">=ROUND(AVERAGE($F$4:$F$101), 2)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t xml:space="preserve">After pressing enter, the average moving range of 3.79 will populate all of the cells in column G. If the average moving range is 4.12, you have forgotten to delete the erroneous moving ranges in cells F14 and F15. 
-Note that the inside the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t>AVERAGE()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t xml:space="preserve"> function, the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t>$</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t xml:space="preserve"> symbol is used to create absolute references. This locks the cell address so it doesn't change when the formula is copied to the other cells in column G. The </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t>AVERAGE()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t xml:space="preserve"> function is wrapped in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t>ROUND()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Montserrat"/>
-      </rPr>
-      <t xml:space="preserve"> function to ensure the result is returned to 2 decimal places.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">To calculate the mean, select cell C3 and enter the formula:
 </t>
     </r>
@@ -1799,12 +1548,263 @@
   <si>
     <t>Raw Data GitHub URL:</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">To calculate the moving ranges, begin by selecting cell </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>F4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t xml:space="preserve"> and entering the equation </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>= ROUND(ABS(B3 - B4), 2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t xml:space="preserve">. This formula calculates the absolute value of the difference between cells B3 (14.6) and B4 (7.5). Because we are working inside a table, Excel automatically copies the formula to all other rows in column F, calculating all of the values of the moving range. 
+Since we are only concerned with the magnitude of the difference between values, the formula wraps the subtraction between successive cells in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>ABS()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t xml:space="preserve"> function. This ensures the result of the subtraction is always positive, never negative. The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>ABS()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t xml:space="preserve"> function is then wrapped in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>ROUND()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t xml:space="preserve"> so we can specify the result is returned to 2 decimal places.
+When the formula is entered correctly, the moving range in cell F4 should be 7.1. 
+Note that cell F3 returns </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>#VALUE!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t xml:space="preserve"> This error is Excel's way of telling you that one of the cells in the formula contains text instead of a number. That is, Excel has attempted to subtract the numeric value in B3 of 14.6 from the text value in B2 of Rate. Since arithmetic between text and numbers is not possible #VALUE! is returned. Select F3 and press delete to remove the error.  
+Note that the values in cells F14 and F15 are also highlighted. Since B14 contains no value, the calculated moving ranges in cells F14 and F15 are erroneous. If they are not deleted they will inflate the average moving range. Thus, to avoid calculating an inflated average moving range, select cells F14 and F15 and press delete.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">To calculate the average moving range, select cell G3 and enter the formula:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t xml:space="preserve">=ROUND(AVERAGE($F$4:$F$101), 2)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t xml:space="preserve">After pressing enter, the average moving range of 3.79 will populate all of the cells in column G. If the average moving range is 4.12, you have forgotten to delete the erroneous moving ranges in cells F14 and F15. 
+Note that inside the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>AVERAGE()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t xml:space="preserve"> function, the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>$</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t xml:space="preserve"> symbol is used to create absolute references. This locks the cell address so it doesn't change when the formula is copied to the other cells in column G. The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>AVERAGE()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t xml:space="preserve"> function is wrapped in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>ROUND()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t xml:space="preserve"> function to ensure the result is returned to 2 decimal places.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Constructing an XmR chart in Excel is achieved in two steps: constructing the X chart and constructing the mR chart. We will begin by constructing the X chart. 
+To construct the X chart select cells A2 through E101. With these cells selected, navigate to the toolbar and select </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>INSERT &gt; CHARTS &gt; LINE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t xml:space="preserve">.
+To construct the mR chart select cells F2 through H101. With these cells selected, navigate to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>INSERT &gt; CHARTS &gt; LINE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>.
+With the charts inserted, format them so that:
+1) Delete the Chart Titles, Legends, and horizontal grid lines. 
+2) Change all of the process limits to a dashed line style and make the color red.
+3) Change the line color for the mean and the average moving range to black. 
+4) Change the marker type for the rates and moving ranges to built in type circle and size 6.
+Additionally, establish conditional formating paramters for the Rate column (B3:B101) so that any cell with a death-to-birth rate that is greater than the UPL or equal to the LPL is highlighted with a light red fill and a dark red text. Also establish conditional formatting for any moving range greater than the URL in the mR column (F4:F101).</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1890,6 +1890,12 @@
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Montserrat"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFC00000"/>
       <name val="Montserrat"/>
     </font>
   </fonts>
@@ -2055,7 +2061,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2183,6 +2189,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -9204,7 +9216,7 @@
     </row>
     <row r="2" spans="1:17" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
@@ -9698,7 +9710,7 @@
       <c r="P27" s="20"/>
       <c r="Q27" s="21"/>
       <c r="S27" s="30" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="T27" s="31"/>
       <c r="U27" s="31"/>
@@ -9724,7 +9736,7 @@
       <c r="P28" s="20"/>
       <c r="Q28" s="21"/>
       <c r="S28" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="T28" s="25"/>
       <c r="U28" s="25"/>
@@ -9750,7 +9762,7 @@
       <c r="P29" s="20"/>
       <c r="Q29" s="21"/>
       <c r="S29" s="27" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="T29" s="28"/>
       <c r="U29" s="28"/>
@@ -9776,7 +9788,7 @@
       <c r="P30" s="20"/>
       <c r="Q30" s="21"/>
       <c r="S30" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="T30" s="8"/>
       <c r="U30" s="8"/>
@@ -9802,7 +9814,7 @@
       <c r="P31" s="20"/>
       <c r="Q31" s="21"/>
       <c r="S31" s="27" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="T31" s="25"/>
       <c r="U31" s="25"/>
@@ -9828,7 +9840,7 @@
       <c r="P32" s="20"/>
       <c r="Q32" s="21"/>
       <c r="S32" s="7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="T32" s="8"/>
       <c r="U32" s="8"/>
@@ -9854,7 +9866,7 @@
       <c r="P33" s="20"/>
       <c r="Q33" s="21"/>
       <c r="S33" s="10" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="T33" s="11"/>
       <c r="U33" s="11"/>
@@ -9880,7 +9892,7 @@
       <c r="P34" s="20"/>
       <c r="Q34" s="21"/>
       <c r="S34" s="30" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="T34" s="36"/>
       <c r="U34" s="36"/>
@@ -10111,7 +10123,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24202841-CFF7-43A9-A3A2-F8F7C7F07F47}">
-  <dimension ref="A1:AA41"/>
+  <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="26" max="26" width="16.5546875" customWidth="1"/>
@@ -10860,28 +10872,46 @@
       <c r="Y40" s="40"/>
     </row>
     <row r="41" spans="10:25" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-      <c r="L41" s="2"/>
-      <c r="M41" s="2"/>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
-      <c r="P41" s="2"/>
-      <c r="Q41" s="2"/>
-      <c r="R41" s="2"/>
-      <c r="S41" s="2"/>
-      <c r="T41" s="2"/>
-      <c r="U41" s="2"/>
-      <c r="V41" s="2"/>
-      <c r="W41" s="2"/>
-      <c r="X41" s="2"/>
-      <c r="Y41" s="2"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="40"/>
+      <c r="N41" s="40"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40"/>
+      <c r="R41" s="40"/>
+      <c r="S41" s="40"/>
+      <c r="T41" s="40"/>
+      <c r="U41" s="40"/>
+      <c r="V41" s="40"/>
+      <c r="W41" s="40"/>
+      <c r="X41" s="40"/>
+      <c r="Y41" s="40"/>
+    </row>
+    <row r="42" spans="10:25" x14ac:dyDescent="0.25">
+      <c r="J42" s="40"/>
+      <c r="K42" s="40"/>
+      <c r="L42" s="40"/>
+      <c r="M42" s="40"/>
+      <c r="N42" s="40"/>
+      <c r="O42" s="40"/>
+      <c r="P42" s="40"/>
+      <c r="Q42" s="40"/>
+      <c r="R42" s="40"/>
+      <c r="S42" s="40"/>
+      <c r="T42" s="40"/>
+      <c r="U42" s="40"/>
+      <c r="V42" s="40"/>
+      <c r="W42" s="40"/>
+      <c r="X42" s="40"/>
+      <c r="Y42" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="J1:Y1"/>
-    <mergeCell ref="J2:Y40"/>
+    <mergeCell ref="J2:Y42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10957,7 +10987,7 @@
         <v>10</v>
       </c>
       <c r="J2" s="40" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="K2" s="40"/>
       <c r="L2" s="40"/>
@@ -12313,7 +12343,7 @@
         <v>10</v>
       </c>
       <c r="J2" s="40" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K2" s="40"/>
       <c r="L2" s="40"/>
@@ -13919,7 +13949,7 @@
       <c r="F1" s="43"/>
       <c r="G1" s="43"/>
       <c r="H1" s="43"/>
-      <c r="J1" s="41" t="s">
+      <c r="J1" s="46" t="s">
         <v>2</v>
       </c>
       <c r="K1" s="42"/>
@@ -13963,7 +13993,7 @@
         <v>10</v>
       </c>
       <c r="J2" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="K2" s="40"/>
       <c r="L2" s="40"/>
@@ -15965,7 +15995,7 @@
       <c r="F1" s="43"/>
       <c r="G1" s="43"/>
       <c r="H1" s="43"/>
-      <c r="J1" s="41" t="s">
+      <c r="J1" s="46" t="s">
         <v>2</v>
       </c>
       <c r="K1" s="42"/>
@@ -16009,7 +16039,7 @@
         <v>10</v>
       </c>
       <c r="J2" s="40" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K2" s="40"/>
       <c r="L2" s="40"/>
@@ -18676,7 +18706,7 @@
         <v>10</v>
       </c>
       <c r="J2" s="40" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="K2" s="40"/>
       <c r="L2" s="40"/>
@@ -19924,7 +19954,7 @@
         <v>12.39</v>
       </c>
       <c r="J30" s="44" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K30" s="44"/>
       <c r="L30" s="44"/>
@@ -20490,7 +20520,7 @@
         <v>12.39</v>
       </c>
       <c r="J42" s="44" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K42" s="45"/>
       <c r="L42" s="45"/>
@@ -22570,7 +22600,7 @@
       <c r="F1" s="43"/>
       <c r="G1" s="43"/>
       <c r="H1" s="43"/>
-      <c r="J1" s="38" t="s">
+      <c r="J1" s="47" t="s">
         <v>115</v>
       </c>
       <c r="K1" s="38"/>
@@ -22614,7 +22644,7 @@
         <v>10</v>
       </c>
       <c r="J2" s="40" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K2" s="40"/>
       <c r="L2" s="40"/>
@@ -25974,19 +26004,19 @@
         <v>117</v>
       </c>
       <c r="C1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H1" t="s">
         <v>4</v>
@@ -26000,7 +26030,7 @@
         <v>119</v>
       </c>
       <c r="C2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D2">
         <v>1841</v>
@@ -26026,7 +26056,7 @@
         <v>119</v>
       </c>
       <c r="C3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D3">
         <v>1841</v>
@@ -26052,7 +26082,7 @@
         <v>119</v>
       </c>
       <c r="C4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D4">
         <v>1841</v>
@@ -26078,7 +26108,7 @@
         <v>119</v>
       </c>
       <c r="C5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D5">
         <v>1841</v>
@@ -26104,7 +26134,7 @@
         <v>119</v>
       </c>
       <c r="C6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D6">
         <v>1841</v>
@@ -26130,7 +26160,7 @@
         <v>119</v>
       </c>
       <c r="C7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D7">
         <v>1841</v>
@@ -26156,7 +26186,7 @@
         <v>119</v>
       </c>
       <c r="C8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D8">
         <v>1841</v>
@@ -26182,7 +26212,7 @@
         <v>119</v>
       </c>
       <c r="C9" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D9">
         <v>1841</v>
@@ -26208,7 +26238,7 @@
         <v>119</v>
       </c>
       <c r="C10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D10">
         <v>1841</v>
@@ -26234,7 +26264,7 @@
         <v>119</v>
       </c>
       <c r="C11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D11">
         <v>1841</v>
@@ -26260,7 +26290,7 @@
         <v>119</v>
       </c>
       <c r="C12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D12">
         <v>1841</v>
@@ -26286,7 +26316,7 @@
         <v>119</v>
       </c>
       <c r="C13" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D13">
         <v>1841</v>
@@ -26303,7 +26333,7 @@
         <v>119</v>
       </c>
       <c r="C14" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D14">
         <v>1842</v>
@@ -26329,7 +26359,7 @@
         <v>119</v>
       </c>
       <c r="C15" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D15">
         <v>1842</v>
@@ -26355,7 +26385,7 @@
         <v>119</v>
       </c>
       <c r="C16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D16">
         <v>1842</v>
@@ -26381,7 +26411,7 @@
         <v>119</v>
       </c>
       <c r="C17" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D17">
         <v>1842</v>
@@ -26407,7 +26437,7 @@
         <v>119</v>
       </c>
       <c r="C18" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D18">
         <v>1842</v>
@@ -26433,7 +26463,7 @@
         <v>119</v>
       </c>
       <c r="C19" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D19">
         <v>1842</v>
@@ -26459,7 +26489,7 @@
         <v>119</v>
       </c>
       <c r="C20" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D20">
         <v>1842</v>
@@ -26485,7 +26515,7 @@
         <v>119</v>
       </c>
       <c r="C21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D21">
         <v>1842</v>
@@ -26511,7 +26541,7 @@
         <v>119</v>
       </c>
       <c r="C22" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D22">
         <v>1842</v>
@@ -26537,7 +26567,7 @@
         <v>119</v>
       </c>
       <c r="C23" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D23">
         <v>1842</v>
@@ -26563,7 +26593,7 @@
         <v>119</v>
       </c>
       <c r="C24" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D24">
         <v>1842</v>
@@ -26589,7 +26619,7 @@
         <v>119</v>
       </c>
       <c r="C25" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D25">
         <v>1842</v>
@@ -26615,7 +26645,7 @@
         <v>119</v>
       </c>
       <c r="C26" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D26">
         <v>1843</v>
@@ -26641,7 +26671,7 @@
         <v>119</v>
       </c>
       <c r="C27" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D27">
         <v>1843</v>
@@ -26667,7 +26697,7 @@
         <v>119</v>
       </c>
       <c r="C28" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D28">
         <v>1843</v>
@@ -26693,7 +26723,7 @@
         <v>119</v>
       </c>
       <c r="C29" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D29">
         <v>1843</v>
@@ -26719,7 +26749,7 @@
         <v>119</v>
       </c>
       <c r="C30" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D30">
         <v>1843</v>
@@ -26745,7 +26775,7 @@
         <v>119</v>
       </c>
       <c r="C31" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D31">
         <v>1843</v>
@@ -26771,7 +26801,7 @@
         <v>119</v>
       </c>
       <c r="C32" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D32">
         <v>1843</v>
@@ -26797,7 +26827,7 @@
         <v>119</v>
       </c>
       <c r="C33" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D33">
         <v>1843</v>
@@ -26823,7 +26853,7 @@
         <v>119</v>
       </c>
       <c r="C34" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D34">
         <v>1843</v>
@@ -26849,7 +26879,7 @@
         <v>119</v>
       </c>
       <c r="C35" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D35">
         <v>1843</v>
@@ -26875,7 +26905,7 @@
         <v>119</v>
       </c>
       <c r="C36" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D36">
         <v>1843</v>
@@ -26901,7 +26931,7 @@
         <v>119</v>
       </c>
       <c r="C37" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D37">
         <v>1843</v>
@@ -26927,7 +26957,7 @@
         <v>119</v>
       </c>
       <c r="C38" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D38">
         <v>1844</v>
@@ -26953,7 +26983,7 @@
         <v>119</v>
       </c>
       <c r="C39" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D39">
         <v>1844</v>
@@ -26979,7 +27009,7 @@
         <v>119</v>
       </c>
       <c r="C40" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D40">
         <v>1844</v>
@@ -27005,7 +27035,7 @@
         <v>119</v>
       </c>
       <c r="C41" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D41">
         <v>1844</v>
@@ -27031,7 +27061,7 @@
         <v>119</v>
       </c>
       <c r="C42" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D42">
         <v>1844</v>
@@ -27057,7 +27087,7 @@
         <v>119</v>
       </c>
       <c r="C43" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D43">
         <v>1844</v>
@@ -27083,7 +27113,7 @@
         <v>119</v>
       </c>
       <c r="C44" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D44">
         <v>1844</v>
@@ -27109,7 +27139,7 @@
         <v>119</v>
       </c>
       <c r="C45" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D45">
         <v>1844</v>
@@ -27135,7 +27165,7 @@
         <v>119</v>
       </c>
       <c r="C46" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D46">
         <v>1844</v>
@@ -27161,7 +27191,7 @@
         <v>119</v>
       </c>
       <c r="C47" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D47">
         <v>1844</v>
@@ -27187,7 +27217,7 @@
         <v>119</v>
       </c>
       <c r="C48" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D48">
         <v>1844</v>
@@ -27213,7 +27243,7 @@
         <v>119</v>
       </c>
       <c r="C49" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D49">
         <v>1844</v>
@@ -27239,7 +27269,7 @@
         <v>119</v>
       </c>
       <c r="C50" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D50">
         <v>1845</v>
@@ -27265,7 +27295,7 @@
         <v>119</v>
       </c>
       <c r="C51" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D51">
         <v>1845</v>
@@ -27291,7 +27321,7 @@
         <v>119</v>
       </c>
       <c r="C52" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D52">
         <v>1845</v>
@@ -27317,7 +27347,7 @@
         <v>119</v>
       </c>
       <c r="C53" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D53">
         <v>1845</v>
@@ -27343,7 +27373,7 @@
         <v>119</v>
       </c>
       <c r="C54" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D54">
         <v>1845</v>
@@ -27369,7 +27399,7 @@
         <v>119</v>
       </c>
       <c r="C55" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D55">
         <v>1845</v>
@@ -27395,7 +27425,7 @@
         <v>119</v>
       </c>
       <c r="C56" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D56">
         <v>1845</v>
@@ -27421,7 +27451,7 @@
         <v>119</v>
       </c>
       <c r="C57" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D57">
         <v>1845</v>
@@ -27447,7 +27477,7 @@
         <v>119</v>
       </c>
       <c r="C58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D58">
         <v>1845</v>
@@ -27473,7 +27503,7 @@
         <v>119</v>
       </c>
       <c r="C59" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D59">
         <v>1845</v>
@@ -27499,7 +27529,7 @@
         <v>119</v>
       </c>
       <c r="C60" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D60">
         <v>1845</v>
@@ -27525,7 +27555,7 @@
         <v>119</v>
       </c>
       <c r="C61" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D61">
         <v>1845</v>
@@ -27551,7 +27581,7 @@
         <v>119</v>
       </c>
       <c r="C62" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D62">
         <v>1846</v>
@@ -27577,7 +27607,7 @@
         <v>119</v>
       </c>
       <c r="C63" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D63">
         <v>1846</v>
@@ -27603,7 +27633,7 @@
         <v>119</v>
       </c>
       <c r="C64" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D64">
         <v>1846</v>
@@ -27629,7 +27659,7 @@
         <v>119</v>
       </c>
       <c r="C65" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D65">
         <v>1846</v>
@@ -27655,7 +27685,7 @@
         <v>119</v>
       </c>
       <c r="C66" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D66">
         <v>1846</v>
@@ -27681,7 +27711,7 @@
         <v>119</v>
       </c>
       <c r="C67" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D67">
         <v>1846</v>
@@ -27707,7 +27737,7 @@
         <v>119</v>
       </c>
       <c r="C68" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D68">
         <v>1846</v>
@@ -27733,7 +27763,7 @@
         <v>119</v>
       </c>
       <c r="C69" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D69">
         <v>1846</v>
@@ -27759,7 +27789,7 @@
         <v>119</v>
       </c>
       <c r="C70" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D70">
         <v>1846</v>
@@ -27785,7 +27815,7 @@
         <v>119</v>
       </c>
       <c r="C71" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D71">
         <v>1846</v>
@@ -27811,7 +27841,7 @@
         <v>119</v>
       </c>
       <c r="C72" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D72">
         <v>1846</v>
@@ -27837,7 +27867,7 @@
         <v>119</v>
       </c>
       <c r="C73" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D73">
         <v>1846</v>
@@ -27863,7 +27893,7 @@
         <v>119</v>
       </c>
       <c r="C74" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D74">
         <v>1847</v>
@@ -27889,7 +27919,7 @@
         <v>119</v>
       </c>
       <c r="C75" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D75">
         <v>1847</v>
@@ -27915,7 +27945,7 @@
         <v>119</v>
       </c>
       <c r="C76" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D76">
         <v>1847</v>
@@ -27941,7 +27971,7 @@
         <v>119</v>
       </c>
       <c r="C77" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D77">
         <v>1847</v>
@@ -27967,7 +27997,7 @@
         <v>119</v>
       </c>
       <c r="C78" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D78">
         <v>1847</v>
@@ -27993,7 +28023,7 @@
         <v>120</v>
       </c>
       <c r="C79" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D79">
         <v>1847</v>
@@ -28019,7 +28049,7 @@
         <v>120</v>
       </c>
       <c r="C80" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D80">
         <v>1847</v>
@@ -28045,7 +28075,7 @@
         <v>120</v>
       </c>
       <c r="C81" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D81">
         <v>1847</v>
@@ -28071,7 +28101,7 @@
         <v>120</v>
       </c>
       <c r="C82" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D82">
         <v>1847</v>
@@ -28097,7 +28127,7 @@
         <v>120</v>
       </c>
       <c r="C83" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D83">
         <v>1847</v>
@@ -28123,7 +28153,7 @@
         <v>120</v>
       </c>
       <c r="C84" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D84">
         <v>1847</v>
@@ -28149,7 +28179,7 @@
         <v>120</v>
       </c>
       <c r="C85" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D85">
         <v>1847</v>
@@ -28175,7 +28205,7 @@
         <v>120</v>
       </c>
       <c r="C86" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D86">
         <v>1848</v>
@@ -28201,7 +28231,7 @@
         <v>120</v>
       </c>
       <c r="C87" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D87">
         <v>1848</v>
@@ -28227,7 +28257,7 @@
         <v>120</v>
       </c>
       <c r="C88" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D88">
         <v>1848</v>
@@ -28253,7 +28283,7 @@
         <v>120</v>
       </c>
       <c r="C89" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D89">
         <v>1848</v>
@@ -28279,7 +28309,7 @@
         <v>120</v>
       </c>
       <c r="C90" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D90">
         <v>1848</v>
@@ -28305,7 +28335,7 @@
         <v>120</v>
       </c>
       <c r="C91" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D91">
         <v>1848</v>
@@ -28331,7 +28361,7 @@
         <v>120</v>
       </c>
       <c r="C92" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D92">
         <v>1848</v>
@@ -28357,7 +28387,7 @@
         <v>120</v>
       </c>
       <c r="C93" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D93">
         <v>1848</v>
@@ -28383,7 +28413,7 @@
         <v>120</v>
       </c>
       <c r="C94" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D94">
         <v>1848</v>
@@ -28409,7 +28439,7 @@
         <v>120</v>
       </c>
       <c r="C95" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D95">
         <v>1848</v>
@@ -28435,7 +28465,7 @@
         <v>120</v>
       </c>
       <c r="C96" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D96">
         <v>1848</v>
@@ -28461,7 +28491,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D97">
         <v>1848</v>
@@ -28487,7 +28517,7 @@
         <v>120</v>
       </c>
       <c r="C98" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D98">
         <v>1849</v>
@@ -28513,7 +28543,7 @@
         <v>120</v>
       </c>
       <c r="C99" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D99">
         <v>1849</v>
@@ -28539,7 +28569,7 @@
         <v>120</v>
       </c>
       <c r="C100" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D100">
         <v>1849</v>
